--- a/samples/ss_cbatu34_mdrcn_ingest.xlsx
+++ b/samples/ss_cbatu34_mdrcn_ingest.xlsx
@@ -767,7 +767,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">

--- a/samples/ss_cbatu34_mdrcn_ingest.xlsx
+++ b/samples/ss_cbatu34_mdrcn_ingest.xlsx
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U58"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -744,7 +744,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBT 3,4 Cibatu 500/150 kV</t>
+          <t>IBT 3 Cibatu 500/150 kV</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -781,14 +781,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 3,4)</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
@@ -823,37 +819,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cibatu 3,4 (bus 150 kV)</t>
+          <t>IBT 4 Cibatu 500/150 kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>IBT 4 CBATU347</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CBATU347</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>CBATU34</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -863,10 +869,14 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -884,12 +894,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jababeka Usin</t>
+          <t>Cibatu 3,4 (bus 150 kV)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JUSIN</t>
+          <t>CBATU34</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -898,7 +908,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -910,7 +920,11 @@
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -941,12 +955,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cilegsi</t>
+          <t>Jababeka Usin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLGSI</t>
+          <t>JUSIN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -998,12 +1012,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maka Sri</t>
+          <t>Cilegsi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MKSRI</t>
+          <t>CLGSI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1034,14 +1048,10 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1059,12 +1069,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kesambi Baru</t>
+          <t>Maka Sri</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KSBRU</t>
+          <t>MKSRI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1095,10 +1105,14 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1116,12 +1130,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pinayungan</t>
+          <t>Kesambi Baru</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PNYNG</t>
+          <t>KSBRU</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1130,7 +1144,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1142,11 +1156,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>GI Simpul 4 subsistem; split busbar + kopel</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
@@ -1156,14 +1166,10 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1181,12 +1187,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Katomukti</t>
+          <t>Pinayungan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KTMKR</t>
+          <t>PNYNG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1207,7 +1213,11 @@
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>GI Simpul 4 subsistem; split busbar + kopel</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
@@ -1217,10 +1227,14 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1238,12 +1252,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maligi</t>
+          <t>Katomukti</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MLIGI</t>
+          <t>KTMKR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1295,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Peruri</t>
+          <t>Maligi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PRURI</t>
+          <t>MLIGI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1309,7 +1323,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1331,14 +1345,10 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1356,12 +1366,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Purwamaya</t>
+          <t>Peruri</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PRMYA</t>
+          <t>PRURI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1392,10 +1402,14 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1413,12 +1427,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tanjung Jabe</t>
+          <t>Purwamaya</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TLJBE</t>
+          <t>PRMYA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1427,7 +1441,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1470,12 +1484,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Honda</t>
+          <t>Tanjung Jabe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HONDA</t>
+          <t>TLJBE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1527,12 +1541,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Indolakto Beauty</t>
+          <t>Honda</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ILBTY</t>
+          <t>HONDA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1541,7 +1555,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1584,12 +1598,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Karang Pawitan</t>
+          <t>Indolakto Beauty</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KRPYG</t>
+          <t>ILBTY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1641,12 +1655,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tegal Tanjung Baru</t>
+          <t>Karang Pawitan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TTJBR</t>
+          <t>KRPYG</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1655,7 +1669,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1698,12 +1712,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Dawuan</t>
+          <t>Tegal Tanjung Baru</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DWUAN</t>
+          <t>TTJBR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1755,17 +1769,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Dawuan</t>
+          <t>Dawuan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IBT 1 DWUAN</t>
+          <t>DWUAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1773,33 +1787,15 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>DWUAN</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>DWUAN4</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
@@ -1809,14 +1805,10 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1834,17 +1826,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Dawuan (bus 70 kV)</t>
+          <t>IBT 150/70 kV Dawuan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DWUAN4</t>
+          <t>IBT 1 DWUAN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1852,17 +1844,31 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>DWUAN</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>DWUAN4</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>bus section + kopel</t>
+          <t>IBT 150/70 kV</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -1874,10 +1880,14 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1895,12 +1905,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rengasdengklok</t>
+          <t>Dawuan (bus 70 kV)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>RDLOK</t>
+          <t>DWUAN4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1909,7 +1919,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1921,7 +1931,11 @@
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
@@ -1931,14 +1945,10 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -1956,12 +1966,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pondok Ali</t>
+          <t>Rengasdengklok</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>PNDLI</t>
+          <t>RDLOK</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1992,10 +2002,14 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2013,25 +2027,25 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GITET Mandirancan</t>
+          <t>Pondok Ali</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MDRCN7</t>
+          <t>PNDLI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>500 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2060,7 +2074,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>MDRCN</t>
+          <t>CBATU34</t>
         </is>
       </c>
     </row>
@@ -2070,51 +2084,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IBT 1,2 Mandirancan 500/150 kV</t>
+          <t>GITET Mandirancan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IBT 1 MDRCN7</t>
+          <t>MDRCN7</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>500/150 kV</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>MDRCN7</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>MDRCN5</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
+          <t>500 kV</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
@@ -2124,14 +2120,10 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2149,31 +2141,45 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mandirancan (bus 150 kV)</t>
+          <t>IBT 1 Mandirancan 500/150 kV</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>IBT 1 MDRCN7</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>IBT 3-Winding</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>MDRCN7</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>MDRCN5</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Busbar GI</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -2185,10 +2191,14 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2206,31 +2216,45 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PLTU Indramayu</t>
+          <t>IBT 2 Mandirancan 500/150 kV</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KIT_IDMYU</t>
+          <t>IBT 2 MDRCN7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>MDRCN7</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>MDRCN5</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -2242,10 +2266,14 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2263,12 +2291,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Indramayu (bus PLTU)</t>
+          <t>Mandirancan (bus 150 kV)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IDMYU5</t>
+          <t>MDRCN5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2299,14 +2327,10 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2324,21 +2348,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Sukamedi</t>
+          <t>PLTU Indramayu</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SKMDI</t>
+          <t>KIT_IDMYU</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Pembangkit</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2381,12 +2405,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Narajiwa</t>
+          <t>Indramayu (bus PLTU)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NARJW</t>
+          <t>IDMYU5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2395,7 +2419,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2417,10 +2441,14 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2438,12 +2466,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Seragi</t>
+          <t>Sukamedi</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SRAGI</t>
+          <t>SKMDI</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2474,14 +2502,10 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2499,12 +2523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Haurgeulis</t>
+          <t>Narajiwa</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HRGLS</t>
+          <t>NARJW</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2513,7 +2537,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2556,12 +2580,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Jatibarang</t>
+          <t>Seragi</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JTBRG</t>
+          <t>SRAGI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2570,7 +2594,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2592,10 +2616,14 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2613,12 +2641,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cikarang Barat</t>
+          <t>Haurgeulis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CKRBR</t>
+          <t>HRGLS</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2649,14 +2677,10 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2674,12 +2698,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cikedung</t>
+          <t>Jatibarang</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CKDNG</t>
+          <t>JTBRG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2688,7 +2712,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2731,51 +2755,33 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IBT 150/70 kV Jatibarang</t>
+          <t>Cikarang Barat</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IBT 1 JTBRG</t>
+          <t>CKRBR</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>JTBRG</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>ARJWN</t>
-        </is>
-      </c>
-      <c r="J36" t="n">
-        <v>2</v>
-      </c>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>IBT 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
@@ -2790,7 +2796,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -2810,12 +2816,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Arjawinangun (bus 70 kV)</t>
+          <t>Cikedung</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ARJWN</t>
+          <t>CKDNG</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2828,7 +2834,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -2836,11 +2842,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>bus section + kopel</t>
-        </is>
-      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
@@ -2871,33 +2873,51 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Indramayu (bus 70 kV)</t>
+          <t>IBT 150/70 kV Jatibarang</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IDMYU</t>
+          <t>IBT 1 JTBRG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>JTBRG</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ARJWN</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>2</v>
+      </c>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>IBT 150/70 kV</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
@@ -2912,7 +2932,7 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -2932,12 +2952,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Semen</t>
+          <t>Arjawinangun (bus 70 kV)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SEMEN</t>
+          <t>ARJWN</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2958,7 +2978,11 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>bus section + kopel</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
@@ -2968,14 +2992,10 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -2993,12 +3013,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kadipaten (bus 70 kV)</t>
+          <t>Indramayu (bus 70 kV)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>KDPTN</t>
+          <t>IDMYU</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3007,7 +3027,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3034,7 +3054,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3054,12 +3074,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sunyaragi</t>
+          <t>Semen</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SYRGI</t>
+          <t>SEMEN</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3068,11 +3088,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -3090,10 +3110,14 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q41" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3111,17 +3135,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>IBT 1,5 Sunyaragi 150/70 kV</t>
+          <t>Kadipaten (bus 70 kV)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IBT 1 SYRGI</t>
+          <t>KDPTN</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>IBT 3-Winding</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -3129,33 +3153,15 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>150/70 kV</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>SYRGI</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>SYRGI4</t>
-        </is>
-      </c>
-      <c r="J42" t="n">
-        <v>2</v>
-      </c>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>IBT 1 &amp; 5 150/70 kV</t>
-        </is>
-      </c>
+      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
@@ -3170,7 +3176,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3190,12 +3196,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sunyaragi (bus 70 kV)</t>
+          <t>Sunyaragi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SYRGI4</t>
+          <t>SYRGI</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3204,11 +3210,11 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -3247,12 +3253,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IBT 2 Sunyaragi 150/66 kV</t>
+          <t>IBT 1 Sunyaragi 150/70 kV</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IBT 2 SYRGI</t>
+          <t>IBT 1 SYRGI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3265,12 +3271,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>150/66 kV</t>
+          <t>150/70 kV</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3280,18 +3286,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SYRGI6</t>
+          <t>SYRGI4</t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>IBT 2 150/66 kV; beda rasio, tidak paralel dengan IBT 1&amp;5</t>
-        </is>
-      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
@@ -3306,7 +3308,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -3326,17 +3328,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sunyaragi (bus 66 kV)</t>
+          <t>IBT 5 Sunyaragi 150/70 kV</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SYRGI6</t>
+          <t>IBT 5 SYRGI</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -3344,13 +3346,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>66 kV</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>150/70 kV</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>SYRGI</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SYRGI4</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
@@ -3362,10 +3378,14 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3383,12 +3403,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kuningan (bus 66 kV)</t>
+          <t>Sunyaragi (bus 70 kV)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KNNGN6</t>
+          <t>SYRGI4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3397,11 +3417,11 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>66 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -3409,11 +3429,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>tegangan primer rendah (risiko 11)</t>
-        </is>
-      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
@@ -3423,14 +3439,10 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3448,33 +3460,51 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Babakan</t>
+          <t>IBT 2 Sunyaragi 150/66 kV</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BBKAN</t>
+          <t>IBT 2 SYRGI</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>70 kV</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>150/66 kV</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>SYRGI</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SYRGI6</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>IBT 2 150/66 kV; beda rasio, tidak paralel dengan IBT 1&amp;5</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
@@ -3489,7 +3519,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -3509,12 +3539,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kuningan</t>
+          <t>Sunyaragi (bus 66 kV)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KNNGN</t>
+          <t>SYRGI6</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3523,11 +3553,11 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>66 kV</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -3545,14 +3575,10 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>13;19</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3570,12 +3596,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hankook (SS Cibatu 1,2)</t>
+          <t>Kuningan (bus 66 kV)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HNKOK</t>
+          <t>KNNGN6</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3584,11 +3610,11 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>66 kV</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -3598,7 +3624,7 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
+          <t>tegangan primer rendah (risiko 11)</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -3607,17 +3633,17 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3625,7 +3651,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>CBATU34</t>
+          <t>MDRCN</t>
         </is>
       </c>
     </row>
@@ -3635,12 +3661,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tegal Herang (SS Deltamas)</t>
+          <t>Babakan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>TGHRG</t>
+          <t>BBKAN</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3649,11 +3675,11 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -3661,28 +3687,24 @@
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3690,7 +3712,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>CBATU34</t>
+          <t>MDRCN</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3722,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Mega Kaya (SS Deltamas)</t>
+          <t>Kuningan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MGKYA</t>
+          <t>KNNGN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3714,11 +3736,11 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -3726,28 +3748,24 @@
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>SOURCE_BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>13;19</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
           <t>Jawa Barat</t>
@@ -3755,7 +3773,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>CBATU34</t>
+          <t>MDRCN</t>
         </is>
       </c>
     </row>
@@ -3765,12 +3783,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Sukatani (SS Sukatani 1,2)</t>
+          <t>Hankook (SS Cibatu 1,2)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SKTNI</t>
+          <t>HNKOK</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3779,7 +3797,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3793,7 +3811,7 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Sukatani 1,2</t>
+          <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -3830,12 +3848,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Padalarang Baru (SS Cirata)</t>
+          <t>Tegal Herang (SS Deltamas)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PDLRU</t>
+          <t>TGHRG</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3844,7 +3862,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3858,7 +3876,7 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Cirata 1,2,3</t>
+          <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -3895,12 +3913,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Purwakarta (SS Cirata)</t>
+          <t>Mega Kaya (SS Deltamas)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PWKTA</t>
+          <t>MGKYA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3909,11 +3927,11 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -3923,7 +3941,7 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Cirata 1,2,3</t>
+          <t>batas ke Subsistem Cibatu 1,2 - Deltamas 1,2</t>
         </is>
       </c>
       <c r="M54" t="inlineStr"/>
@@ -3960,12 +3978,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Indramayu Barat (SS Cirata)</t>
+          <t>Sukatani (SS Sukatani 1,2)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IDBRT</t>
+          <t>SKTNI</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3974,11 +3992,11 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -3988,7 +4006,7 @@
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Cirata 1,2,3</t>
+          <t>batas ke Subsistem Sukatani 1,2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -4025,12 +4043,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Curug (SS Cirata)</t>
+          <t>Padalarang Baru (SS Cirata)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CURUG</t>
+          <t>PDLRU</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4039,11 +4057,11 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>70 kV</t>
+          <t>150 kV</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -4090,12 +4108,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Parakan (SS New Ujungberung)</t>
+          <t>Purwakarta (SS Cirata)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PRKAN</t>
+          <t>PWKTA</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4104,7 +4122,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4118,7 +4136,7 @@
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>batas ke Subsistem Bandung Selatan - New Ujungberung</t>
+          <t>batas ke Subsistem Cirata 1,2,3</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -4145,7 +4163,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>MDRCN</t>
+          <t>CBATU34</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4173,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kesambi Baru (sisi Mandirancan)</t>
+          <t>Indramayu Barat (SS Cirata)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KSBRU_M</t>
+          <t>IDBRT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4169,11 +4187,11 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>70 kV</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -4183,7 +4201,7 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>batas ke sisi Cibatu 3,4</t>
+          <t>batas ke Subsistem Cirata 1,2,3</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -4209,6 +4227,201 @@
         </is>
       </c>
       <c r="S58" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Curug (SS Cirata)</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CURUG</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Cirata 1,2,3</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Parakan (SS New Ujungberung)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PRKAN</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>70 kV</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>batas ke Subsistem Bandung Selatan - New Ujungberung</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>MDRCN</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Kesambi Baru (sisi Mandirancan)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>KSBRU_M</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Busbar GI</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>batas ke sisi Cibatu 3,4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>SOURCE_BOUNDARY</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Jawa Barat</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
         <is>
           <t>MDRCN</t>
         </is>
@@ -7362,12 +7575,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[N-1] 1. SUTT 150 kV Cibatu- Mekarsari 1,2 sudah berbeban diatas 60% (@88%, N-1 tidak terpenuhi). Apabila pasokan PLTU Indramayu &lt;400 MW, maka ruas SUTT 150 kV Cibatu-Mekarsari akan mengalami Overload. 2. Terdapat potensi Power swing pada subsistem Cibatu 3,4-PLTU Indramayu- Mandirancan 1,2 apabila terjadi N-2 pada ruas SUTT 150 kV Cibatu- Mekarsari</t>
+          <t>[N-2] 1. SUTT 150 kV Cibatu- Mekarsari 1,2 sudah berbeban diatas 60% (@88%, N-1 tidak terpenuhi). Apabila pasokan PLTU Indramayu &lt;400 MW, maka ruas SUTT 150 kV Cibatu-Mekarsari akan mengalami Overload. 2. Terdapat potensi Power swing pada subsistem Cibatu 3,4-PLTU Indramayu- Mandirancan 1,2 apabila terjadi N-2 pada ruas SUTT 150 kV Cibatu- Mekarsari</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7397,12 +7610,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[N-1] 1. SUTT 150 kV Mekarsari- Pinayungan 1,2 sudah berbeban diatas 60% (@78%, N-1 tidak terpenuhi). Apabila pasokan PLTU Indramayu &lt;400 MW, maka ruas SUTT 150 kV Mekarsari- Pinayungan akan mengalami Overload. 2. Terdapat potensi Power swing pada subsistem Cibatu 3,4-PLTU Indramayu- Mandirancan 1,2 apabila terjadi N-2 pada ruas SUTT 150 kV Mekarsari- Pinayungan</t>
+          <t>[N-2] 1. SUTT 150 kV Mekarsari- Pinayungan 1,2 sudah berbeban diatas 60% (@78%, N-1 tidak terpenuhi). Apabila pasokan PLTU Indramayu &lt;400 MW, maka ruas SUTT 150 kV Mekarsari- Pinayungan akan mengalami Overload. 2. Terdapat potensi Power swing pada subsistem Cibatu 3,4-PLTU Indramayu- Mandirancan 1,2 apabila terjadi N-2 pada ruas SUTT 150 kV Mekarsari- Pinayungan</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7432,12 +7645,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[N-1] 1. SUTT 150 kV Pinayungan- Peruri/Parungmulya sudah berbeban diatas 60% (@77%, N-1 tidak terpenuhi). Apabila pasokan PLTU Indramayu &lt;280 MW, maka ruas SUTT 150 kV Pinayungan- Peruri/Parungmulya akan mengalami Overload. 2. Terdapat potensi Power swing pada subsistem Cibatu 3,4-PLTU Indramayu- Mandirancan 1,2 apabila terjadi N-2 pada ruas SUTT 150 kV Pinayungan- Peruri/Parungmulya</t>
+          <t>[N-2] 1. SUTT 150 kV Pinayungan- Peruri/Parungmulya sudah berbeban diatas 60% (@77%, N-1 tidak terpenuhi). Apabila pasokan PLTU Indramayu &lt;280 MW, maka ruas SUTT 150 kV Pinayungan- Peruri/Parungmulya akan mengalami Overload. 2. Terdapat potensi Power swing pada subsistem Cibatu 3,4-PLTU Indramayu- Mandirancan 1,2 apabila terjadi N-2 pada ruas SUTT 150 kV Pinayungan- Peruri/Parungmulya</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7537,12 +7750,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] IBT 1,2 GITET Mandirancan sudah berbeban &gt;60% (@87%) saat PLTU CEP atau PLTU Indramayu outage</t>
+          <t>[BELUM_DITETAPKAN] IBT 1,2 GITET Mandirancan sudah berbeban &gt;60% (@87%) saat PLTU CEP atau PLTU Indramayu outage</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7607,12 +7820,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>N-2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] SUTT 150 kV Indramayu-Sukamandi 1,2 terdapat bottleneck pada CrossBar sebesar 1600 A, sedangkan kapasitas SUTT sebesar 2780 A per sirkit. Apabila terjadi kontingensi N-2 pada SUTT 150 kV Indramayu-Kosambi Baru, maka ruas SUTT 150 kV Indramayu- Sukamandi 1,2 akan berpotensi Overload</t>
+          <t>[N-2] SUTT 150 kV Indramayu-Sukamandi 1,2 terdapat bottleneck pada CrossBar sebesar 1600 A, sedangkan kapasitas SUTT sebesar 2780 A per sirkit. Apabila terjadi kontingensi N-2 pada SUTT 150 kV Indramayu-Kosambi Baru, maka ruas SUTT 150 kV Indramayu- Sukamandi 1,2 akan berpotensi Overload</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7677,12 +7890,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[N-1] IBT-2 150/66 kV Sunyaragi tidak bisa operasi parallel dengan IBT-1&amp;5 150/70 kV dikarenakan beda rasio tegangan, yang menyebabkan tegangan primer di GI Kuningan juga rendah, tegangan maksimal yang bisa dicapai saat beban puncak hanya sebesar 68 kV dengan posisi tap OLTC di 16/17</t>
+          <t>[BELUM_DITETAPKAN] IBT-2 150/66 kV Sunyaragi tidak bisa operasi parallel dengan IBT-1&amp;5 150/70 kV dikarenakan beda rasio tegangan, yang menyebabkan tegangan primer di GI Kuningan juga rendah, tegangan maksimal yang bisa dicapai saat beban puncak hanya sebesar 68 kV dengan posisi tap OLTC di 16/17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7712,12 +7925,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[N-1] Hanya terdapat 1 (satu) IBT-4 150/70 kV Jatibarang. Kondisi saat ini IBT-4 Jatibarang operasi radial memasok ke GI 70 kV Indramayu (trafo-1&amp;3) dan busbar A GI 70 kV Arjawinangun (trafo- 1,2&amp;3)</t>
+          <t>[BELUM_DITETAPKAN] Hanya terdapat 1 (satu) IBT-4 150/70 kV Jatibarang. Kondisi saat ini IBT-4 Jatibarang operasi radial memasok ke GI 70 kV Indramayu (trafo-1&amp;3) dan busbar A GI 70 kV Arjawinangun (trafo- 1,2&amp;3)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -7957,12 +8170,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>N-1</t>
+          <t>BELUM_DITETAPKAN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan tinggi pada Trafo-2 GI 70 kV Kuningan terutama saat periode libur hari raya (Idul Fitri, Idul Adha dan Nataru)</t>
+          <t>[BELUM_DITETAPKAN] Pembebanan tinggi pada Trafo-2 GI 70 kV Kuningan terutama saat periode libur hari raya (Idul Fitri, Idul Adha dan Nataru)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">

--- a/samples/ss_cbatu34_mdrcn_ingest.xlsx
+++ b/samples/ss_cbatu34_mdrcn_ingest.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Views" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gardu_Induk_dan_Aset" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jalur_Transmisi" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bay" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data_Kerawanan_Detail" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7489,6 +7490,600 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Kode GI</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Nama GI</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Feeder (GI Induk)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Tegangan</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Jumlah Sirkit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Status Operasi</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>No Kerawanan</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sudut Pandang</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HNKOK</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hankook (SS Cibatu 1,2)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SKMDI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sukamedi (SS Mandirancan 1,2)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>IDMYU5</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PDLRU</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Padalarang Baru (SS Cirata)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TTJBR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SKTNI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sukatani (SS Sukatani 1,2)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DWUAN</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>TGHRG</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tegal Herang (SS Deltamas)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PNYNG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MGKYA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mega Kaya (SS Deltamas)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PNYNG</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ILBTY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Indolakto Beauty</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MLIGI</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IDBRT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Indramayu Barat (SS Cirata)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PNDLI</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PWKTA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Purwakarta (SS Cirata)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PNDLI</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CURUG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Curug (SS Cirata)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>RDLOK</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>CBATU34</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KSBRU</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Kesambi Baru (sisi Cibatu 3,4)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>IDMYU5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>MDRCN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PRKAN</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Parakan (SS New Ujungberung)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KDPTN</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SUTT</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>MDRCN</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
